--- a/output/企业标签全量表_2026-07-16_V20.xlsx
+++ b/output/企业标签全量表_2026-07-16_V20.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1329"/>
+  <dimension ref="A1:I1333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,12 +778,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>睡眠监测;康复器械;可穿戴监测</t>
+          <t>跌倒监测;睡眠监测</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>睡眠监测;可穿戴监测</t>
+          <t>跌倒监测</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>可穿戴监测</t>
+          <t>跌倒监测</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>睡眠监测;可穿戴监测;紧急呼叫</t>
+          <t>跌倒监测;睡眠监测</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>适老化</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>康复辅具</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>康复器械</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>养老机构;康复医疗</t>
+          <t>康复医疗</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>养老服务;消费品</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>居家护理;个人护理</t>
+          <t>个人护理</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>养老服务;行业服务</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>居家护理;养老信息平台</t>
+          <t>养老机构</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>助听器;助行器;医疗器械</t>
+          <t>医疗器械</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11544,12 +11544,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>诊所</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -12017,12 +12017,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>养老服务;康复辅具</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>可穿戴监测</t>
+          <t>助行器;适老化</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>养老机构;康复医疗</t>
+          <t>康复医疗</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -13178,12 +13178,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>轮椅;助行器</t>
+          <t>个人护理</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -13393,12 +13393,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>轮椅;助行器</t>
+          <t>诊所</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>助行器;轮椅</t>
+          <t>医疗器械</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -15375,12 +15375,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>轮椅;助行器</t>
+          <t>诊所</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -16063,12 +16063,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>行业服务</t>
+          <t>文娱社交</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>兴趣社群</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -16837,12 +16837,12 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>轮椅;助行器</t>
+          <t>诊所</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -20505,12 +20505,12 @@
       <c r="B470" t="inlineStr"/>
       <c r="C470" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -22040,7 +22040,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>中医养生</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -23522,12 +23522,12 @@
       <c r="B545" t="inlineStr"/>
       <c r="C545" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -23683,7 +23683,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -25045,7 +25045,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>适老化</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -25473,12 +25473,12 @@
       <c r="B594" t="inlineStr"/>
       <c r="C594" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>陪伴服务</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -25512,17 +25512,17 @@
       <c r="B595" t="inlineStr"/>
       <c r="C595" t="inlineStr">
         <is>
-          <t>行业服务</t>
+          <t>康复辅具</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>医疗器械</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>面向银发经济的行业服务企业，围绕尿失禁等方向开展相关服务，连接养老产业上下游资源，海外（主要面向欧美等市场）市场，服务于银发产业从业者、服务机构与中老年消费群体</t>
+          <t>德国柏林的老年护理智能失禁监测方案商。核心产品 Sensa 系统：一次性传感贴片监测失禁用者的干湿状态，实时向护理人员推送提醒，帮助养老机构减少渗漏与压疮。B2B 面向临床与护理机构。</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -25984,12 +25984,12 @@
       <c r="B607" t="inlineStr"/>
       <c r="C607" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -26067,12 +26067,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>面向银发经济的行业服务企业，围绕智慧养老等方向开展相关服务，连接养老产业上下游资源，海外（主要面向欧美等市场）市场，服务于银发产业从业者、服务机构与中老年消费群体</t>
+          <t>由 Castlight（医疗导航）与 Vera Whole Health（进阶初级护理）于2022年合并而成的医疗科技公司，提供数据驱动的健康导航平台+进阶初级护理中心，服务含老年在内的风险人群，按价值医疗（VBC）模式运营。B2B 健康平台。</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
@@ -26184,12 +26184,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>面向银发经济的行业服务企业，围绕尿失禁等方向开展相关服务，连接养老产业上下游资源，海外（主要面向欧美等市场）市场，服务于银发产业从业者、服务机构与中老年消费群体</t>
+          <t>德国柏林的护理数字化 SaaS 厂商。核心产品 alea 系统：基于传感夹+IoT+AI，实时监测失禁状态、跌倒与体位并自动生成护理记录，已获 CE 医疗器械认证，服务多家养老院。B2B 护理机构软件。</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -26296,12 +26296,12 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>兴趣社群;陪伴服务</t>
+          <t>远程护理</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -26379,12 +26379,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>面向银发经济的行业服务企业，围绕平台等方向开展相关服务，连接养老产业上下游资源，海外（主要面向欧美等市场）市场，服务于银发产业从业者、服务机构与中老年消费群体</t>
+          <t>美国家庭医疗与临终关怀机构的 AI 排班与劳动力管理 SaaS。通过智能路线规划、实时可见性与患者互动提升临床团队利用率、降低缺诊率，已与主流 EMR 集成。B2B 医疗运营软件。</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
@@ -26925,7 +26925,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>慢病管理</t>
+          <t>居家护理</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -27154,12 +27154,12 @@
       <c r="B637" t="inlineStr"/>
       <c r="C637" t="inlineStr">
         <is>
-          <t>养老服务;文娱社交</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>远程医疗;陪伴服务</t>
+          <t>远程医疗</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -27193,12 +27193,12 @@
       <c r="B638" t="inlineStr"/>
       <c r="C638" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>居家护理;护理协调</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -27271,12 +27271,12 @@
       <c r="B640" t="inlineStr"/>
       <c r="C640" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>专业护理;居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -27739,12 +27739,12 @@
       <c r="B652" t="inlineStr"/>
       <c r="C652" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>兴趣社群;陪伴服务</t>
+          <t>远程医疗</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -27778,12 +27778,12 @@
       <c r="B653" t="inlineStr"/>
       <c r="C653" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -27973,12 +27973,12 @@
       <c r="B658" t="inlineStr"/>
       <c r="C658" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>兴趣社群;陪伴服务</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>安宁疗护;居家护理</t>
+          <t>安宁疗护</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -28051,12 +28051,12 @@
       <c r="B660" t="inlineStr"/>
       <c r="C660" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -28285,12 +28285,12 @@
       <c r="B666" t="inlineStr"/>
       <c r="C666" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>兴趣社群;陪伴服务</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -28402,12 +28402,12 @@
       <c r="B669" t="inlineStr"/>
       <c r="C669" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>兴趣社群;陪伴服务</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -28835,12 +28835,12 @@
       <c r="B680" t="inlineStr"/>
       <c r="C680" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>陪伴服务</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -29030,12 +29030,12 @@
       <c r="B685" t="inlineStr"/>
       <c r="C685" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -29147,17 +29147,17 @@
       <c r="B688" t="inlineStr"/>
       <c r="C688" t="inlineStr">
         <is>
-          <t>行业服务</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>尿失禁</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>面向银发经济的行业服务企业，围绕尿失禁等方向开展相关服务，连接养老产业上下游资源，海外（主要面向欧美等市场）市场，服务于银发产业从业者、服务机构与中老年消费群体</t>
+          <t>美国 Pelvital 旗下 FDA 认证的居家盆底康复器械，针对女性压力性尿失禁（SUI），通过经阴道机械振动疗法强化盆底肌，5分钟/天、6周见效，处方与自费双渠道。面向消费者的医疗器械。</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
@@ -29264,12 +29264,12 @@
       <c r="B691" t="inlineStr"/>
       <c r="C691" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>兴趣社群;陪伴服务</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -29386,7 +29386,7 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
@@ -29619,12 +29619,12 @@
       <c r="B700" t="inlineStr"/>
       <c r="C700" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>居家护理;SDOH</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -30048,12 +30048,12 @@
       <c r="B711" t="inlineStr"/>
       <c r="C711" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -30087,12 +30087,12 @@
       <c r="B712" t="inlineStr"/>
       <c r="C712" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>居家护理;远程护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
@@ -30291,7 +30291,7 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>居家护理;家政</t>
+          <t>护工平台</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
@@ -30451,7 +30451,7 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>护工平台;居家护理</t>
+          <t>护工平台</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -30490,7 +30490,7 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>护工平台;居家护理</t>
+          <t>护工平台</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -30563,12 +30563,12 @@
       <c r="B724" t="inlineStr"/>
       <c r="C724" t="inlineStr">
         <is>
-          <t>养老服务;文娱社交</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>慢病管理;陪伴服务</t>
+          <t>慢病管理</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
@@ -30680,12 +30680,12 @@
       <c r="B727" t="inlineStr"/>
       <c r="C727" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>兴趣社群;陪伴服务</t>
+          <t>远程护理</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
@@ -30763,7 +30763,7 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
@@ -30992,12 +30992,12 @@
       <c r="B735" t="inlineStr"/>
       <c r="C735" t="inlineStr">
         <is>
-          <t>行业服务</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>适老化</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -31153,7 +31153,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>康复医疗</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -31187,12 +31187,12 @@
       <c r="B740" t="inlineStr"/>
       <c r="C740" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>兴趣社群;陪伴服务</t>
+          <t>远程护理</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -31265,12 +31265,12 @@
       <c r="B742" t="inlineStr"/>
       <c r="C742" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>居家护理;护理协调</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
@@ -31655,12 +31655,12 @@
       <c r="B752" t="inlineStr"/>
       <c r="C752" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>居家护理;护理协调</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
@@ -34003,12 +34003,12 @@
       <c r="B812" t="inlineStr"/>
       <c r="C812" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>陪伴服务</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -34393,12 +34393,12 @@
       <c r="B822" t="inlineStr"/>
       <c r="C822" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
@@ -34553,12 +34553,12 @@
       <c r="B826" t="inlineStr"/>
       <c r="C826" t="inlineStr">
         <is>
-          <t>行业服务;食品营养</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>养老咨询;膳食配送</t>
+          <t>膳食配送</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
@@ -35255,12 +35255,12 @@
       <c r="B844" t="inlineStr"/>
       <c r="C844" t="inlineStr">
         <is>
-          <t>养老服务;文娱社交</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>远程医疗;陪伴服务</t>
+          <t>远程医疗</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
@@ -35498,7 +35498,7 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
@@ -36078,12 +36078,12 @@
       <c r="B865" t="inlineStr"/>
       <c r="C865" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>陪伴服务</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
@@ -36316,12 +36316,12 @@
       <c r="B871" t="inlineStr"/>
       <c r="C871" t="inlineStr">
         <is>
-          <t>行业服务</t>
+          <t>金融保险</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>行业研究</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
@@ -37069,17 +37069,17 @@
       <c r="B890" t="inlineStr"/>
       <c r="C890" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>陪伴服务</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>面向银发（中老年）人群的老年文娱领域企业，主营社交平台业务：面向中老年及照护群体的社交、陪伴与社区互动</t>
+          <t>面向言语障碍人群（含中风、帕金森等导致的老年失语患者）的语音识别AI解决方案，通过机器学习识别非标准语音并转换为清晰语音，帮助失语老人重新沟通。采用B2B技术授权+面向终端用户的App模式。</t>
         </is>
       </c>
       <c r="F890" t="inlineStr">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>可穿戴监测</t>
+          <t>紧急呼叫</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -39141,12 +39141,12 @@
       <c r="B942" t="inlineStr"/>
       <c r="C942" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -39380,7 +39380,7 @@
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
@@ -39618,7 +39618,7 @@
       </c>
       <c r="D954" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E954" t="inlineStr">
@@ -40834,12 +40834,12 @@
       <c r="B985" t="inlineStr"/>
       <c r="C985" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
@@ -41146,12 +41146,12 @@
       <c r="B993" t="inlineStr"/>
       <c r="C993" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>陪伴服务</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
@@ -41302,12 +41302,12 @@
       <c r="B997" t="inlineStr"/>
       <c r="C997" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
@@ -41619,7 +41619,7 @@
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
@@ -41692,12 +41692,12 @@
       <c r="B1007" t="inlineStr"/>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>养老服务;行业服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>居家护理;养老信息平台</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
@@ -41736,7 +41736,7 @@
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
@@ -42126,7 +42126,7 @@
       </c>
       <c r="D1018" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1018" t="inlineStr">
@@ -42160,12 +42160,12 @@
       <c r="B1019" t="inlineStr"/>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
@@ -42433,12 +42433,12 @@
       <c r="B1026" t="inlineStr"/>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>养老服务;金融保险</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>居家护理;长护险</t>
+          <t>护工平台</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
@@ -42672,7 +42672,7 @@
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>可穿戴监测</t>
+          <t>跌倒监测</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
@@ -44011,12 +44011,12 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1064" t="inlineStr">
@@ -45300,12 +45300,12 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1095" t="inlineStr">
@@ -46100,12 +46100,12 @@
       <c r="B1115" t="inlineStr"/>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1115" t="inlineStr">
@@ -46139,12 +46139,12 @@
       <c r="B1116" t="inlineStr"/>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1116" t="inlineStr">
@@ -46339,7 +46339,7 @@
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1121" t="inlineStr">
@@ -47244,12 +47244,12 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>养老服务;康复辅具</t>
+          <t>康复辅具</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
-          <t>居家护理;助行器</t>
+          <t>助行器;医疗器械</t>
         </is>
       </c>
       <c r="E1143" t="inlineStr">
@@ -48057,12 +48057,12 @@
       <c r="B1162" t="inlineStr"/>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>行业服务</t>
+          <t>康复辅具</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>助听器</t>
         </is>
       </c>
       <c r="E1162" t="inlineStr">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="D1169" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
@@ -48632,7 +48632,7 @@
       </c>
       <c r="D1176" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1176" t="inlineStr">
@@ -50069,7 +50069,7 @@
       </c>
       <c r="D1211" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1211" t="inlineStr">
@@ -50103,12 +50103,12 @@
       <c r="B1212" t="inlineStr"/>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1212" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1212" t="inlineStr">
@@ -50142,12 +50142,12 @@
       <c r="B1213" t="inlineStr"/>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1213" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1213" t="inlineStr">
@@ -50220,12 +50220,12 @@
       <c r="B1215" t="inlineStr"/>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1215" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1215" t="inlineStr">
@@ -50259,12 +50259,12 @@
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1216" t="inlineStr">
         <is>
-          <t>居家护理;护理协调</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1216" t="inlineStr">
@@ -50298,12 +50298,12 @@
       <c r="B1217" t="inlineStr"/>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1217" t="inlineStr">
@@ -50848,12 +50848,12 @@
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1231" t="inlineStr">
@@ -51048,7 +51048,7 @@
       </c>
       <c r="D1236" t="inlineStr">
         <is>
-          <t>可穿戴监测</t>
+          <t>跌倒监测</t>
         </is>
       </c>
       <c r="E1236" t="inlineStr">
@@ -51710,12 +51710,12 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1253" t="inlineStr">
@@ -51827,12 +51827,12 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1256" t="inlineStr">
@@ -51952,12 +51952,12 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>康复辅具</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>跌倒监测</t>
         </is>
       </c>
       <c r="E1259" t="inlineStr">
@@ -53167,7 +53167,7 @@
       </c>
       <c r="D1289" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1289" t="inlineStr">
@@ -53362,7 +53362,7 @@
       </c>
       <c r="D1294" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1294" t="inlineStr">
@@ -53780,7 +53780,7 @@
       </c>
       <c r="D1304" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1304" t="inlineStr">
@@ -54329,12 +54329,12 @@
       <c r="B1318" t="inlineStr"/>
       <c r="C1318" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="D1318" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="E1318" t="inlineStr">
@@ -54373,7 +54373,7 @@
       </c>
       <c r="D1319" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>居家护理</t>
         </is>
       </c>
       <c r="E1319" t="inlineStr">
@@ -54563,12 +54563,12 @@
       <c r="B1324" t="inlineStr"/>
       <c r="C1324" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="D1324" t="inlineStr">
         <is>
-          <t>可穿戴监测</t>
+          <t>智能家居</t>
         </is>
       </c>
       <c r="E1324" t="inlineStr">
@@ -54641,12 +54641,12 @@
       <c r="B1326" t="inlineStr"/>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="D1326" t="inlineStr">
         <is>
-          <t>可穿戴监测</t>
+          <t>智能家居</t>
         </is>
       </c>
       <c r="E1326" t="inlineStr">
@@ -54685,7 +54685,7 @@
       </c>
       <c r="D1327" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>养老机构</t>
         </is>
       </c>
       <c r="E1327" t="inlineStr">
@@ -54724,7 +54724,7 @@
       </c>
       <c r="D1328" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="E1328" t="inlineStr">
@@ -54763,7 +54763,7 @@
       </c>
       <c r="D1329" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="E1329" t="inlineStr">
@@ -54787,6 +54787,162 @@
         </is>
       </c>
       <c r="I1329" t="inlineStr"/>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>红松 Hongsong</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr"/>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>文娱社交</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>兴趣社群</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>国内退休人群文娱直播课社区头部，提供兴趣课程+社交直播，模式反常识标杆；已完成A+轮。</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>B2C银发文娱社区</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>服务商(媒体/数据)</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr"/>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>携程老友会</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr"/>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>文娱社交</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>旅游</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>国内银发旅游头部品牌（携程旗下），“老有意思旅行团”六大主题游；450万+会员、7000+线路，携程增长最快业务模块之一。</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>B2C银发旅游</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>服务商(媒体/数据)</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr"/>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>Silversurfers</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr"/>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>文娱社交</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>英国最大50+在线社区，30万+注册、社媒100万+关注，UGC活力老人内容（论坛/展示/交友）。</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>UGC活力老人社区</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>服务商(媒体/数据)</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>Whispp</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr"/>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>行业服务</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>养老软件</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>语音重建AI，助言语障碍老人恢复自然声音；2026-07-07获LUMO Labs领投融资。</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>B2C语音重建AI</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>服务商(媒体/数据)</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -54799,7 +54955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54836,7 +54992,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -54852,15 +55008,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>适老化</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>养护院、养老机构、养老机构SaaS、养老院、养老院中介、托老院、护理院、护理院运营商、敬老院、机构养老、照护机构</t>
+          <t>居家适老、无障碍适老、老年友好、适老、适老化、适老化改造咨询、适老化服务、出行、老人出行、助老交通、老年用车、非紧急医疗转运</t>
         </is>
       </c>
     </row>
@@ -54872,15 +55028,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>适老化</t>
+          <t>养老机构</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>居家适老、无障碍适老、老年友好、适老、适老化、适老化改造咨询、适老化服务、出行、老人出行、助老交通、老年用车、非紧急医疗转运</t>
+          <t>养护院、养老机构、养老机构SaaS、养老院、养老院中介、托老院、护理院、护理院运营商、敬老院、机构养老、照护机构</t>
         </is>
       </c>
     </row>
@@ -54916,7 +55072,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -54936,7 +55092,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -54952,15 +55108,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>护士上门</t>
+          <t>远程医疗</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>护士上门、护士到家</t>
+          <t>RPM、互联网医疗、医养结合、在线诊疗、居家医疗AI平台、虚拟、虚拟/面对面、虚拟健康、虚拟咨询、虚拟监护、远程医疗、远程患者照护、远程检查、远程照护、远程监控、远程营养</t>
         </is>
       </c>
     </row>
@@ -54972,15 +55128,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>安宁疗护</t>
+          <t>远程护理</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>临终关怀、安宁疗护、缓和医疗</t>
+          <t>数字护理协调、虚拟护理、虚拟护理协调、虚拟护理平台、远程护理、远程护理协调</t>
         </is>
       </c>
     </row>
@@ -54992,7 +55148,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>远程医疗</t>
+          <t>护士上门</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -55000,7 +55156,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RPM、互联网医疗、医养结合、在线诊疗、居家医疗AI平台、虚拟、虚拟/面对面、虚拟健康、虚拟咨询、虚拟监护、远程医疗、远程患者照护、远程检查、远程照护、远程监控、远程营养</t>
+          <t>护士上门、护士到家</t>
         </is>
       </c>
     </row>
@@ -55012,15 +55168,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>安宁疗护</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>护理协调、护理协调SaaS、护理调度、护理转介、照护转介、转诊平台</t>
+          <t>临终关怀、安宁疗护、缓和医疗</t>
         </is>
       </c>
     </row>
@@ -55032,7 +55188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>远程护理</t>
+          <t>护工平台</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -55040,7 +55196,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>数字护理协调、虚拟护理、虚拟护理协调、虚拟护理平台、远程护理、远程护理协调</t>
+          <t>护工平台、护工撮合、照护匹配</t>
         </is>
       </c>
     </row>
@@ -55072,7 +55228,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>远程监护</t>
+          <t>康复医疗</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -55080,7 +55236,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>远程健康监护、远程监护</t>
+          <t>AR神经康复、养老康复、可穿戴康复、居家康复/远程康复、康复医疗、康复设备、手部康复、数字康复、数字治疗、数字疗法、智能康复、神经康复、肿瘤康复、脑机接口康复、运动康复</t>
         </is>
       </c>
     </row>
@@ -55092,15 +55248,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>康复医疗</t>
+          <t>远程监护</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AR神经康复、养老康复、可穿戴康复、居家康复/远程康复、康复医疗、康复设备、手部康复、数字康复、数字治疗、数字疗法、智能康复、神经康复、肿瘤康复、脑机接口康复、运动康复</t>
+          <t>远程健康监护、远程监护</t>
         </is>
       </c>
     </row>
@@ -55132,15 +55288,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>护工平台</t>
+          <t>CCRC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>护工平台、护工撮合、照护匹配</t>
+          <t>CCRC、持续照料社区、持续照料退休社区</t>
         </is>
       </c>
     </row>
@@ -55152,7 +55308,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CCRC</t>
+          <t>心理健康</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -55160,7 +55316,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CCRC、持续照料社区、持续照料退休社区</t>
+          <t>VR培训、VR疗法、孤独干预、心理健康、心理健康服务、心理咨询、抑郁、焦虑/抑郁、睡眠CBT、睡眠呼吸、睡眠诊断、神经助眠、精神健康、行为激活</t>
         </is>
       </c>
     </row>
@@ -55172,15 +55328,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>护理协调</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VR培训、VR疗法、孤独干预、心理健康、心理健康服务、心理咨询、抑郁、焦虑/抑郁、睡眠CBT、睡眠呼吸、睡眠诊断、神经助眠、精神健康、行为激活</t>
+          <t>护理协调、护理协调SaaS、护理调度、护理转介、照护转介、转诊平台</t>
         </is>
       </c>
     </row>
@@ -55236,7 +55392,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -55256,7 +55412,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -55276,7 +55432,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -55312,7 +55468,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>照护支持</t>
+          <t>中医养生</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -55320,7 +55476,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>家属照护支持、护理者支持、照护者支持</t>
+          <t>中医保健、中医养生、中医理疗养生</t>
         </is>
       </c>
     </row>
@@ -55332,7 +55488,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>护士派遣</t>
+          <t>照护支持</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -55340,7 +55496,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>临床护士配置、护士外派、护士派遣</t>
+          <t>家属照护支持、护理者支持、照护者支持</t>
         </is>
       </c>
     </row>
@@ -55352,15 +55508,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>陪诊</t>
+          <t>护士派遣</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>医院陪护、就医陪同、就医陪诊、就诊陪同、陪同就医、陪诊、陪诊服务</t>
+          <t>临床护士配置、护士外派、护士派遣</t>
         </is>
       </c>
     </row>
@@ -55372,7 +55528,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中医养生</t>
+          <t>陪诊</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -55380,7 +55536,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>中医保健、中医养生、中医理疗养生</t>
+          <t>医院陪护、就医陪同、就医陪诊、就诊陪同、陪同就医、陪诊、陪诊服务</t>
         </is>
       </c>
     </row>
@@ -55456,7 +55612,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -55476,7 +55632,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -55492,15 +55648,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>康复器械</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>wheelchair、手动轮椅、智能轮椅、电动轮椅、轮椅、轮椅车</t>
+          <t>康复器材、康复器械、康复辅助器具、理疗器械、辅助器具、适老辅具、呼吸、呼吸慢病、慢阻肺</t>
         </is>
       </c>
     </row>
@@ -55512,15 +55668,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>轮椅</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>康复器材、康复器械、康复辅助器具、理疗器械、辅助器具、适老辅具、呼吸、呼吸慢病、慢阻肺</t>
+          <t>wheelchair、手动轮椅、智能轮椅、电动轮椅、轮椅、轮椅车</t>
         </is>
       </c>
     </row>
@@ -55532,15 +55688,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>跌倒监测</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>睡眠健康、睡眠监测、睡眠追踪</t>
+          <t>AI防跌倒、PERS、摔倒监测、跌倒/行为监测、跌倒检测、跌倒监测、跌倒预警、防跌倒、防跌监测</t>
         </is>
       </c>
     </row>
@@ -55552,15 +55708,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>睡眠监测</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AI防跌倒、PERS、摔倒监测、跌倒/行为监测、跌倒检测、跌倒监测、跌倒预警、防跌倒、防跌监测</t>
+          <t>睡眠健康、睡眠监测、睡眠追踪</t>
         </is>
       </c>
     </row>
@@ -55632,7 +55788,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>医疗器械</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -55640,7 +55796,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> companion robot、AI语音护理记录、云端机器人、人形机器人康养应用、具身养老机器人、具身智能通用平台、养老机器人、养老陪伴人形机器人、医疗服务机器人、医疗机器人、医院机器人、居家服务机器人、康养机器人、康复机器人、护理机器人、护理自动化、日常辅助机器人、服务机器人、机器人、机器人关节模组、治疗机器人、老年机器人、训练机器人、通用具身智能大模型、配送机器人、陪伴机器人</t>
+          <t>医疗器械、医疗用品、医疗设备、家用医疗、家用医疗设备(HME)、数字药房、病炊配送</t>
         </is>
       </c>
     </row>
@@ -55652,15 +55808,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>人形机器人</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>人形机器人、类人机器人</t>
+          <t xml:space="preserve"> companion robot、AI语音护理记录、云端机器人、人形机器人康养应用、具身养老机器人、具身智能通用平台、养老机器人、养老陪伴人形机器人、医疗服务机器人、医疗机器人、医院机器人、居家服务机器人、康养机器人、康复机器人、护理机器人、护理自动化、日常辅助机器人、服务机器人、机器人、机器人关节模组、治疗机器人、老年机器人、训练机器人、通用具身智能大模型、配送机器人、陪伴机器人</t>
         </is>
       </c>
     </row>
@@ -55672,15 +55828,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>智能药盒</t>
+          <t>人形机器人</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>智能药盒、智能药箱、电子药盒</t>
+          <t>人形机器人、类人机器人</t>
         </is>
       </c>
     </row>
@@ -55692,15 +55848,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>紧急呼叫</t>
+          <t>智能药盒</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SOS呼叫、紧急呼叫、紧急呼救</t>
+          <t>智能药盒、智能药箱、电子药盒</t>
         </is>
       </c>
     </row>
@@ -55712,7 +55868,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>紧急呼叫</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -55720,7 +55876,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>医疗器械、医疗用品、医疗设备、家用医疗、家用医疗设备(HME)、数字药房、病炊配送</t>
+          <t>SOS呼叫、紧急呼叫、紧急呼救</t>
         </is>
       </c>
     </row>
@@ -55892,15 +56048,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>眼镜</t>
+          <t>个人护理</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AR字幕眼镜、人工视网膜、眼科、眼镜、老花眼、老花镜、自动调节眼镜、视力检测、视力测试、视觉健康、视觉障碍</t>
+          <t>个人卫生、个人护理、个护、假发、头皮修护、头皮护理、抗衰护肤、日用、染发剂、男士护肤、皮肤长寿、老年护肤</t>
         </is>
       </c>
     </row>
@@ -55912,7 +56068,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>个人护理</t>
+          <t>眼镜</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -55920,7 +56076,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>个人卫生、个人护理、个护、假发、头皮修护、头皮护理、抗衰护肤、日用、染发剂、男士护肤、皮肤长寿、老年护肤</t>
+          <t>AR字幕眼镜、人工视网膜、眼科、眼镜、老花眼、老花镜、自动调节眼镜、视力检测、视力测试、视觉健康、视觉障碍</t>
         </is>
       </c>
     </row>
@@ -55956,7 +56112,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -55992,7 +56148,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>视觉辅助</t>
+          <t>智能家居</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -56000,7 +56156,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>低视力辅助、视觉辅助、视觉辅助设备</t>
+          <t>智能家居、智能居家、环境传感</t>
         </is>
       </c>
     </row>
@@ -56012,15 +56168,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>垂直电商</t>
+          <t>视觉辅助</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>垂直电商、垂类电商、细分品类电商</t>
+          <t>低视力辅助、视觉辅助、视觉辅助设备</t>
         </is>
       </c>
     </row>
@@ -56032,15 +56188,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>智能家居</t>
+          <t>垂直电商</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>智能家居、智能居家、环境传感</t>
+          <t>垂直电商、垂类电商、细分品类电商</t>
         </is>
       </c>
     </row>
@@ -56096,7 +56252,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -56116,7 +56272,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -56196,7 +56352,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -56256,7 +56412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -56512,15 +56668,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老软件</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>养老咨询、养老服务咨询、养老顾问</t>
+          <t>养老SaaS、养老系统、养老软件、照护SaaS、养老信息化、养老运营系统、senior care software、care management software</t>
         </is>
       </c>
     </row>
@@ -56536,7 +56692,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -56552,15 +56708,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>行业媒体</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>B2C媒体、信息目录、内容媒体、媒体、数字营销、营销媒体、行业媒体、行业资讯</t>
+          <t>养老信息平台、养老信息门户、养老平台、养老目录、养老、养老服务、养老产业、elderly care、senior care、养老业务、银发服务</t>
         </is>
       </c>
     </row>
@@ -56572,15 +56728,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>养老信息平台</t>
+          <t>行业媒体</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>养老信息平台、养老信息门户、养老平台、养老目录、养老、养老服务、养老产业、elderly care、senior care、养老业务、银发服务</t>
+          <t>B2C媒体、信息目录、内容媒体、媒体、数字营销、营销媒体、行业媒体、行业资讯</t>
         </is>
       </c>
     </row>
@@ -56612,35 +56768,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>行业研究</t>
+          <t>养老咨询</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>产业研究、行业报告、行业研究</t>
+          <t>养老咨询、养老服务咨询、养老顾问</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>行业服务</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>金融理财</t>
+          <t>行业研究</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>理财、财务规划、财富管理、资产配置、金融理财</t>
+          <t>产业研究、行业报告、行业研究</t>
         </is>
       </c>
     </row>
@@ -56652,15 +56808,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>金融理财</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Medicare Advantage、保险、保险(MA)/初级保健、保险助手、保险服务、保险经纪、医疗保险、医疗保险+诊所、医疗保险计划、医疗险</t>
+          <t>理财、财务规划、财富管理、资产配置、金融理财</t>
         </is>
       </c>
     </row>
@@ -56672,15 +56828,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>保险科技</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>InsurTech、保险科技、保险科技平台、保险科技服务、保险科技解决方案</t>
+          <t>Medicare Advantage、保险、保险(MA)/初级保健、保险助手、保险服务、保险经纪、医疗保险、医疗保险+诊所、医疗保险计划、医疗险</t>
         </is>
       </c>
     </row>
@@ -56692,15 +56848,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>遗产规划</t>
+          <t>保险科技</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>财富传承、身后事规划、遗产规划、遗产记录</t>
+          <t>InsurTech、保险科技、保险科技平台、保险科技服务、保险科技解决方案</t>
         </is>
       </c>
     </row>
@@ -56712,35 +56868,35 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>长护险</t>
+          <t>遗产规划</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>长护险、长护险经办、长期护理险经办</t>
+          <t>财富传承、身后事规划、遗产规划、遗产记录</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>投资机构</t>
+          <t>金融保险</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>产业基金</t>
+          <t>长护险</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>产业基金、产业投资基金、私募股权基金、银发产业基金</t>
+          <t>长护险、长护险经办、长期护理险经办</t>
         </is>
       </c>
     </row>
@@ -56752,15 +56908,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>产业基金</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VC、Venture Capital、养老科技VC、创业投资、创投基金、医疗健康投资、老年服务VC、风险投资</t>
+          <t>产业基金、产业投资基金、私募股权基金、银发产业基金</t>
         </is>
       </c>
     </row>
@@ -56772,13 +56928,33 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>16</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VC、Venture Capital、养老科技VC、创业投资、创投基金、医疗健康投资、老年服务VC、风险投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>投资机构</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>养老REIT</t>
         </is>
       </c>
-      <c r="C99" t="n">
+      <c r="C100" t="n">
         <v>12</v>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t xml:space="preserve"> healthcare REIT、 senior housing REIT、养老REIT、养老地产REIT、医疗REIT、医疗地产信托</t>
         </is>
